--- a/docs/V0_progress.xlsx
+++ b/docs/V0_progress.xlsx
@@ -63,22 +63,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -677,29 +677,29 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>暂不处理</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>待联调</t>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>已联调</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>策划 / UI / 前端</t>
+          <t>策划 / 前端 / 后端</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>UI 已明确入口页是登录成功后的承接页，但是否最终保留仍待 PM / 策划拍板。</t>
+          <t>入口页已能显示真实后端在线状态和聚合玩家数据，但“是否最终保留入口页”仍待 PM / 策划拍板。</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>先按现有入口页继续承接流程；若决定收口，再改成登录后直达章节页。</t>
+          <t>PM 与策划尽快拍板入口页是否保留；若不保留，前端再把流转收口为登录后直达章节页。</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -739,9 +739,9 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>待联调</t>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>已联调</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>前端已接入玩家资料、章节列表和当前章节接口，但还缺一次真实运行中的完整联调验证。</t>
+          <t>前后端真实链路已打通并完成验证；当前主要风险转为后续章节推进和战斗结算继续扩展时，是否保持同样的接口驱动原则。</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>优先验证 `/api/player/profile`、`/api/player/chapters`、`/api/player/current-chapter` 的真实联调链路。</t>
+          <t>继续把后续主页、战斗、结算相关页面统一纳入同一套真实资料与章节进度接口链路。</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -786,7 +786,7 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
@@ -796,9 +796,9 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>待联调</t>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>UI 已补当前章节、已解锁、未解锁、战力不足、加载失败和空数据说明；前端骨架已起，但还需继续收口体验。</t>
+          <t>章节页已改成真实接口驱动，但前端体验细节和与后续战斗入口的衔接还在收口中。</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>前端继续完善章节列表展示、解锁态、当前章节切换和异常态细节。</t>
+          <t>前端继续完善章节列表展示、解锁态、当前章节切换、异常态和进入战斗前的页面衔接。</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -838,12 +838,12 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>暂不处理</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>暂不处理</t>
         </is>
@@ -900,17 +900,17 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
@@ -957,34 +957,34 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>暂不处理</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>前端 / 后端</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>策划和 UI 已收口为数值型功法优先，前端已启动骨架页，但真实玩法数据和升级能力仍未进入首轮实现。</t>
+          <t>后端已提供真实功法列表接口，但前端目前仍主要是骨架页和空态说明，尚未把真实列表完整展示出来。</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>前端先完成只读展示、空态和详情回退规则；升级按钮是否开放继续等待拍板。</t>
+          <t>前端优先接通 `player/skills` 数据，完成真实功法列表、空态和详情回退规则；升级按钮是否开放继续等待拍板。</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1014,17 +1014,17 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>暂不处理</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
@@ -1071,19 +1071,19 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>前端已起可进入的占位场景，但还不是真战斗；后端仍未启动战斗链路，且 README 当前基线仍需控制范围。</t>
+          <t>后端已补齐最小战斗会话接口，但前端当前仍以占位场景为主，HUD、暂停、结算回流体验还未完全接通。</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>先按“章节推进 -&gt; 自动战斗占位 -&gt; 失败重试”做最小骨架，再决定何时拉起后端战斗支持。</t>
+          <t>前端优先接通战斗会话读取、开局和结算回流接口；后端继续配合补最小缺口，不扩散前端伪业务数据。</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1128,19 +1128,19 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>待联调</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>依赖战斗主流程；策划和 UI 口径已补齐，但前后端都还未进入实际开发。</t>
+          <t>后端已具备最小结算回流能力，但前端还没有把成功/失败结算页面和回流体验真正接上。</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>与战斗主流程一并排到下一阶段，先补最小成功/失败结算回流。</t>
+          <t>前端在战斗页联调后优先补最小成功/失败结算页，并对接战斗结算回流接口。</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1180,12 +1180,12 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>暂不处理</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>暂不处理</t>
         </is>
@@ -1232,7 +1232,7 @@
           <t>V0</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>暂不处理</t>
         </is>
@@ -1242,17 +1242,17 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>暂不处理</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>待联调</t>
         </is>
@@ -1310,7 +1310,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
@@ -1322,7 +1322,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
@@ -1346,7 +1346,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>待联调</t>
         </is>
@@ -1394,7 +1394,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>暂不处理</t>
         </is>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>前端正在启动 V0 骨架实现；后端已完成账号、玩家资料、章节进度与真实落库链路；策划和 UI 已完成本轮补充。</t>
+          <t>前后端已补齐账号、主页、章节、功法列表和战斗最小数据链路；下一步重点是继续做页面联调收口、调试能力和更完整的战斗结算体验。</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>后续每次角色提交涉及模块推进时，同步更新本表对应行。</t>
+          <t>后续每次角色提交涉及模块推进时，同步更新本表对应行，并优先检查前端页面是否完全改成以后端接口驱动。</t>
         </is>
       </c>
     </row>
